--- a/Project-2/TestScenario_SauceDemo.xlsx
+++ b/Project-2/TestScenario_SauceDemo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADARSH J. MISHRA\OneDrive\GitHub-Backup\Manual-Testing-Projects\Project-2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d09b73bd954f8bef/GitHub-Backup/Manual-Testing-Projects/Project-2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8134D4F3-0D94-4D59-BC84-9586F3F5E83E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{8134D4F3-0D94-4D59-BC84-9586F3F5E83E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23D02E85-907C-452F-99CE-A589F1DA7E82}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AE7A96EB-CAF4-4974-9235-C6F64EFA36B0}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="77">
   <si>
     <t>Login Module</t>
   </si>
@@ -60,9 +60,6 @@
     <t>Login</t>
   </si>
   <si>
-    <t>Verify login with valid username and password</t>
-  </si>
-  <si>
     <t>High</t>
   </si>
   <si>
@@ -87,24 +84,12 @@
     <t>TS_05</t>
   </si>
   <si>
-    <t>Verify login with invalid username</t>
-  </si>
-  <si>
-    <t>Verify login with invalid password</t>
-  </si>
-  <si>
     <t>TS_06</t>
   </si>
   <si>
     <t>TS_07</t>
   </si>
   <si>
-    <t>Verify login with empty password</t>
-  </si>
-  <si>
-    <t>Verify login with empty username</t>
-  </si>
-  <si>
     <t>TS_08</t>
   </si>
   <si>
@@ -120,9 +105,6 @@
     <t>Verify login of all accepted users with invalid password</t>
   </si>
   <si>
-    <t>Verify login with invalid username and password</t>
-  </si>
-  <si>
     <t>TS_11</t>
   </si>
   <si>
@@ -273,25 +255,19 @@
     <t>Verify product price</t>
   </si>
   <si>
-    <t>TS_32</t>
-  </si>
-  <si>
-    <t>TS_33</t>
-  </si>
-  <si>
     <t>Verify order confirmation after finish</t>
   </si>
   <si>
-    <t>TS_34</t>
-  </si>
-  <si>
     <t>Verify user can go directly product page after back to home button on order confirmation page</t>
   </si>
   <si>
-    <t>TS_35</t>
-  </si>
-  <si>
     <t>Verify user can go login page after clicking logout</t>
+  </si>
+  <si>
+    <t>Verify login with valid credentials</t>
+  </si>
+  <si>
+    <t>Verify login with invalid credentials</t>
   </si>
 </sst>
 </file>
@@ -445,7 +421,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -454,6 +430,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -473,12 +452,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -802,7 +775,7 @@
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.33203125" customWidth="1"/>
@@ -812,18 +785,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="6"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="7"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="7"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="9"/>
+      <c r="A2" s="8"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="10"/>
     </row>
     <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
@@ -847,156 +820,101 @@
         <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>7</v>
+        <v>75</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D2"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1016,135 +934,136 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="6"/>
+      <c r="A1" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="7"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="7"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="9"/>
+      <c r="A2" s="8"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="10"/>
     </row>
     <row r="4" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>8</v>
+      <c r="A11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D2"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1161,115 +1080,115 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="6"/>
+      <c r="A1" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="7"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="7"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="9"/>
+      <c r="A2" s="8"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="10"/>
     </row>
     <row r="4" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1296,185 +1215,185 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="6"/>
+      <c r="A1" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="7"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="7"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="9"/>
+      <c r="A2" s="8"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="10"/>
     </row>
     <row r="4" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>8</v>
+        <v>63</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>8</v>
+        <v>65</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>8</v>
+        <v>67</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>8</v>
+        <v>69</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/Project-2/TestScenario_SauceDemo.xlsx
+++ b/Project-2/TestScenario_SauceDemo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d09b73bd954f8bef/GitHub-Backup/Manual-Testing-Projects/Project-2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{8134D4F3-0D94-4D59-BC84-9586F3F5E83E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23D02E85-907C-452F-99CE-A589F1DA7E82}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{8134D4F3-0D94-4D59-BC84-9586F3F5E83E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20E1AB74-865F-4A99-9C7C-4F4AF38C1CEB}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AE7A96EB-CAF4-4974-9235-C6F64EFA36B0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AE7A96EB-CAF4-4974-9235-C6F64EFA36B0}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="81">
   <si>
     <t>Login Module</t>
   </si>
@@ -135,18 +135,9 @@
     <t>TS_14</t>
   </si>
   <si>
-    <t>Profile</t>
-  </si>
-  <si>
     <t>TS_15</t>
   </si>
   <si>
-    <t>Verify users can add product to cart</t>
-  </si>
-  <si>
-    <t>Verify users can remove product from cart</t>
-  </si>
-  <si>
     <t>TS_16</t>
   </si>
   <si>
@@ -261,13 +252,34 @@
     <t>Verify user can go directly product page after back to home button on order confirmation page</t>
   </si>
   <si>
-    <t>Verify user can go login page after clicking logout</t>
-  </si>
-  <si>
     <t>Verify login with valid credentials</t>
   </si>
   <si>
     <t>Verify login with invalid credentials</t>
+  </si>
+  <si>
+    <t>Verify footer links</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>TS_32</t>
+  </si>
+  <si>
+    <t>Verify product page redirection through image and name</t>
+  </si>
+  <si>
+    <t>TS_33</t>
+  </si>
+  <si>
+    <t>Verify user can add product to cart</t>
+  </si>
+  <si>
+    <t>Verify user can remove product from cart through remove</t>
+  </si>
+  <si>
+    <t>Verify user can redirect to login page after clicking logout</t>
   </si>
 </sst>
 </file>
@@ -421,7 +433,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -452,6 +464,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -820,7 +835,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>7</v>
@@ -834,7 +849,7 @@
         <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>7</v>
@@ -924,13 +939,13 @@
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="56" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -994,7 +1009,7 @@
         <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>30</v>
@@ -1008,10 +1023,10 @@
         <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>12</v>
@@ -1025,7 +1040,7 @@
         <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>12</v>
@@ -1039,7 +1054,7 @@
         <v>26</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>12</v>
@@ -1053,10 +1068,38 @@
         <v>26</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>74</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1081,7 +1124,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -1109,13 +1152,13 @@
     </row>
     <row r="5" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>7</v>
@@ -1123,13 +1166,13 @@
     </row>
     <row r="6" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>7</v>
@@ -1137,13 +1180,13 @@
     </row>
     <row r="7" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>7</v>
@@ -1151,13 +1194,13 @@
     </row>
     <row r="8" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>12</v>
@@ -1165,13 +1208,13 @@
     </row>
     <row r="9" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>12</v>
@@ -1179,13 +1222,13 @@
     </row>
     <row r="10" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>7</v>
@@ -1216,7 +1259,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -1244,13 +1287,13 @@
     </row>
     <row r="5" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>12</v>
@@ -1258,13 +1301,13 @@
     </row>
     <row r="6" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>7</v>
@@ -1272,13 +1315,13 @@
     </row>
     <row r="7" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>7</v>
@@ -1286,13 +1329,13 @@
     </row>
     <row r="8" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>7</v>
@@ -1300,13 +1343,13 @@
     </row>
     <row r="9" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>7</v>
@@ -1314,13 +1357,13 @@
     </row>
     <row r="10" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>7</v>
@@ -1328,13 +1371,13 @@
     </row>
     <row r="11" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>12</v>
@@ -1342,13 +1385,13 @@
     </row>
     <row r="12" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>7</v>
@@ -1356,13 +1399,13 @@
     </row>
     <row r="13" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>7</v>
@@ -1370,13 +1413,13 @@
     </row>
     <row r="14" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>7</v>
@@ -1384,13 +1427,13 @@
     </row>
     <row r="15" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>7</v>

--- a/Project-2/TestScenario_SauceDemo.xlsx
+++ b/Project-2/TestScenario_SauceDemo.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d09b73bd954f8bef/GitHub-Backup/Manual-Testing-Projects/Project-2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{8134D4F3-0D94-4D59-BC84-9586F3F5E83E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20E1AB74-865F-4A99-9C7C-4F4AF38C1CEB}"/>
+  <xr:revisionPtr revIDLastSave="528" documentId="13_ncr:1_{8134D4F3-0D94-4D59-BC84-9586F3F5E83E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79F5B37B-F997-4474-AB5B-AA989A373543}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AE7A96EB-CAF4-4974-9235-C6F64EFA36B0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{AE7A96EB-CAF4-4974-9235-C6F64EFA36B0}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
     <sheet name="Product" sheetId="2" r:id="rId2"/>
     <sheet name="Cart" sheetId="3" r:id="rId3"/>
-    <sheet name="Checkout" sheetId="4" r:id="rId4"/>
+    <sheet name="Checkout - Your Information" sheetId="4" r:id="rId4"/>
+    <sheet name="Checkout - Overview" sheetId="5" r:id="rId5"/>
+    <sheet name="Checkout - Complete" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="169">
   <si>
     <t>Login Module</t>
   </si>
@@ -156,102 +158,51 @@
     <t>Cart</t>
   </si>
   <si>
-    <t>Verify user can go back to product page</t>
-  </si>
-  <si>
     <t>TS_19</t>
   </si>
   <si>
-    <t>Verify overall ui like cart icon , labels, product details</t>
-  </si>
-  <si>
     <t>TS_20</t>
   </si>
   <si>
-    <t>Verify functionality of checkout button</t>
-  </si>
-  <si>
     <t>TS_21</t>
   </si>
   <si>
-    <t>Verify user can remove product</t>
-  </si>
-  <si>
     <t>TS_22</t>
   </si>
   <si>
-    <t>Verify added products visible in cart</t>
-  </si>
-  <si>
     <t>TS_23</t>
   </si>
   <si>
     <t>Verify cart number behaviour</t>
   </si>
   <si>
-    <t>Checkout Module</t>
-  </si>
-  <si>
     <t>TS_24</t>
   </si>
   <si>
-    <t>Checkout</t>
-  </si>
-  <si>
-    <t>Verify overall ui like cancel, checkout button, brand name</t>
-  </si>
-  <si>
     <t>TS_25</t>
   </si>
   <si>
-    <t>Verify user can go back by cancel</t>
-  </si>
-  <si>
     <t>TS_26</t>
   </si>
   <si>
-    <t>Verify error message of all empty field</t>
-  </si>
-  <si>
     <t>TS_27</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify three input field for first name, last name and zip/postal code </t>
-  </si>
-  <si>
     <t>TS_28</t>
   </si>
   <si>
-    <t>Verify checkout on all valid input</t>
-  </si>
-  <si>
     <t>TS_29</t>
   </si>
   <si>
-    <t>Verify checkout on all invalid input</t>
-  </si>
-  <si>
     <t>TS_30</t>
   </si>
   <si>
-    <t>Verify error message of invalid input</t>
-  </si>
-  <si>
     <t>TS_31</t>
   </si>
   <si>
     <t>Verify product details</t>
   </si>
   <si>
-    <t>Verify product price</t>
-  </si>
-  <si>
-    <t>Verify order confirmation after finish</t>
-  </si>
-  <si>
-    <t>Verify user can go directly product page after back to home button on order confirmation page</t>
-  </si>
-  <si>
     <t>Verify login with valid credentials</t>
   </si>
   <si>
@@ -280,6 +231,321 @@
   </si>
   <si>
     <t>Verify user can redirect to login page after clicking logout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify overall ui </t>
+  </si>
+  <si>
+    <t>Verify product redirection through product name</t>
+  </si>
+  <si>
+    <t>Verify footer ui and redirection</t>
+  </si>
+  <si>
+    <t>Verify no product text message on empty cart</t>
+  </si>
+  <si>
+    <t>TS_34</t>
+  </si>
+  <si>
+    <t>TS_35</t>
+  </si>
+  <si>
+    <t>TS_36</t>
+  </si>
+  <si>
+    <t>Verify added products</t>
+  </si>
+  <si>
+    <t>Verify functionality of buttons</t>
+  </si>
+  <si>
+    <t>Verify cart persists behaviour on refresh, logout and login</t>
+  </si>
+  <si>
+    <t>Checkout-Your Information Module</t>
+  </si>
+  <si>
+    <t>Checkout - Your Information</t>
+  </si>
+  <si>
+    <t>Verify user can access checkout information page on 0,1 and more than 1 cart item</t>
+  </si>
+  <si>
+    <t>Verify footer element and content visibility</t>
+  </si>
+  <si>
+    <t>Verify footer link redirection to correct platform</t>
+  </si>
+  <si>
+    <t>Verify the correct number of items displayed in the cart during checkout</t>
+  </si>
+  <si>
+    <t>Verify hamburger button shows all items, logout, about and reset app state options</t>
+  </si>
+  <si>
+    <t>Verify swag labs brand name visibility</t>
+  </si>
+  <si>
+    <t>Verify checkout your information label visibility</t>
+  </si>
+  <si>
+    <t>TS_37</t>
+  </si>
+  <si>
+    <t>Verify cart icon and number of items visibility</t>
+  </si>
+  <si>
+    <t>TS_38</t>
+  </si>
+  <si>
+    <t>Verify input fields first name,last name and postal code visbility</t>
+  </si>
+  <si>
+    <t>TS_39</t>
+  </si>
+  <si>
+    <t>Verify user can enter data in first name,last name and postal code input fields</t>
+  </si>
+  <si>
+    <t>Verify system allows user to overview page on invalid, blank input</t>
+  </si>
+  <si>
+    <t>Verify error message of blank first name field "Error: First Name is required"</t>
+  </si>
+  <si>
+    <t>TS_40</t>
+  </si>
+  <si>
+    <t>TS_41</t>
+  </si>
+  <si>
+    <t>TS_42</t>
+  </si>
+  <si>
+    <t>TS_43</t>
+  </si>
+  <si>
+    <t>TS_44</t>
+  </si>
+  <si>
+    <t>Verify error message of blank last name field "Error: Last Name is required"</t>
+  </si>
+  <si>
+    <t>Verify error message of blank postal code field "Error: Postal code is required"</t>
+  </si>
+  <si>
+    <t>TS_45</t>
+  </si>
+  <si>
+    <t>Verify user redirected to cart after clicking cancel button</t>
+  </si>
+  <si>
+    <t>Verify user can redirect to checkout overview page after clicking continue button on valid input</t>
+  </si>
+  <si>
+    <t>Verify user redirected to item page after clicking all items button</t>
+  </si>
+  <si>
+    <t>Verify user redirected to login page after clicking logout button</t>
+  </si>
+  <si>
+    <t>Verify user redirected to about page of sauce demo after clicking about button</t>
+  </si>
+  <si>
+    <t>Verify number of item displayed in cart during checkout 0 after clicking reset app state button</t>
+  </si>
+  <si>
+    <t>Checkout - Overview Module</t>
+  </si>
+  <si>
+    <t>TS_47</t>
+  </si>
+  <si>
+    <t>TS_46</t>
+  </si>
+  <si>
+    <t>Checkout - Overview</t>
+  </si>
+  <si>
+    <t>Verify user can access checkout overview page on 0,1 and more than 1 cart item</t>
+  </si>
+  <si>
+    <t>TS_48</t>
+  </si>
+  <si>
+    <t>Verify user redirected to items page after clicking cancel button</t>
+  </si>
+  <si>
+    <t>TS_49</t>
+  </si>
+  <si>
+    <t>TS_50</t>
+  </si>
+  <si>
+    <t>TS_51</t>
+  </si>
+  <si>
+    <t>TS_52</t>
+  </si>
+  <si>
+    <t>TS_53</t>
+  </si>
+  <si>
+    <t>Verify user redirected to cart page after clicking cart button</t>
+  </si>
+  <si>
+    <t>TS_54</t>
+  </si>
+  <si>
+    <t>TS_55</t>
+  </si>
+  <si>
+    <t>TS_56</t>
+  </si>
+  <si>
+    <t>TS_57</t>
+  </si>
+  <si>
+    <t>TS_58</t>
+  </si>
+  <si>
+    <t>TS_59</t>
+  </si>
+  <si>
+    <t>TS_60</t>
+  </si>
+  <si>
+    <t>TS_61</t>
+  </si>
+  <si>
+    <t>TS_62</t>
+  </si>
+  <si>
+    <t>Verify qty of each item displayed 1</t>
+  </si>
+  <si>
+    <t>TS_63</t>
+  </si>
+  <si>
+    <t>TS_64</t>
+  </si>
+  <si>
+    <t>Verify user redirected to item page after clicking item name</t>
+  </si>
+  <si>
+    <t>TS_65</t>
+  </si>
+  <si>
+    <t>TS_66</t>
+  </si>
+  <si>
+    <t>Verify brand name swag labs is clearly visible</t>
+  </si>
+  <si>
+    <t>Verify checkout : overview page label is clearly visible</t>
+  </si>
+  <si>
+    <t>Verify Quantity(QTY) and description label clearly visible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify correct item name is visible </t>
+  </si>
+  <si>
+    <t>Verify correct item description is visible</t>
+  </si>
+  <si>
+    <t>Verify correct item price is visible in dollar</t>
+  </si>
+  <si>
+    <t>TS_67</t>
+  </si>
+  <si>
+    <t>Verify payment information is visible with correct information</t>
+  </si>
+  <si>
+    <t>TS_68</t>
+  </si>
+  <si>
+    <t>Verify shipping information is visible with correct information</t>
+  </si>
+  <si>
+    <t>TS_69</t>
+  </si>
+  <si>
+    <t>Verify price total is visible with correct item total and tax in dollar</t>
+  </si>
+  <si>
+    <t>TS_70</t>
+  </si>
+  <si>
+    <t>Verify correct total is visible in dollar</t>
+  </si>
+  <si>
+    <t>Checkout - Complete Module</t>
+  </si>
+  <si>
+    <t>TS_71</t>
+  </si>
+  <si>
+    <t>Checkout - Complete</t>
+  </si>
+  <si>
+    <t>TS_72</t>
+  </si>
+  <si>
+    <t>Verify user redirected to cart page with no item after clicking cart button</t>
+  </si>
+  <si>
+    <t>TS_73</t>
+  </si>
+  <si>
+    <t>Verify user redirected to all item page after clicking back home button</t>
+  </si>
+  <si>
+    <t>TS_74</t>
+  </si>
+  <si>
+    <t>Verify user redirected to complete page after clicking finish button on 0,1 and multiple item</t>
+  </si>
+  <si>
+    <t>TS_75</t>
+  </si>
+  <si>
+    <t>TS_76</t>
+  </si>
+  <si>
+    <t>TS_77</t>
+  </si>
+  <si>
+    <t>TS_78</t>
+  </si>
+  <si>
+    <t>Verify Checkout : Complete page label is clearly visible</t>
+  </si>
+  <si>
+    <t>TS_79</t>
+  </si>
+  <si>
+    <t>Verify green tick successful image is visible</t>
+  </si>
+  <si>
+    <t>TS_80</t>
+  </si>
+  <si>
+    <t>Verify correct thank you message is visible</t>
+  </si>
+  <si>
+    <t>TS_81</t>
+  </si>
+  <si>
+    <t>TS_82</t>
+  </si>
+  <si>
+    <t>Verify user still present on complete page after refresh</t>
+  </si>
+  <si>
+    <t>Verify cart icon does not display item count after order completion</t>
   </si>
 </sst>
 </file>
@@ -433,7 +699,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -446,6 +712,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -464,9 +736,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -800,18 +1069,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="9"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="8"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="10"/>
+      <c r="A2" s="10"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="12"/>
     </row>
     <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
@@ -835,7 +1104,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>7</v>
@@ -849,7 +1118,7 @@
         <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>7</v>
@@ -949,18 +1218,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="9"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="8"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="10"/>
+      <c r="A2" s="10"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="12"/>
     </row>
     <row r="4" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
@@ -1026,7 +1295,7 @@
         <v>26</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>12</v>
@@ -1040,7 +1309,7 @@
         <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>12</v>
@@ -1054,7 +1323,7 @@
         <v>26</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>12</v>
@@ -1082,7 +1351,7 @@
         <v>26</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>7</v>
@@ -1092,14 +1361,14 @@
       <c r="A13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>74</v>
+      <c r="C13" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1116,25 +1385,25 @@
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="44.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="9"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="8"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="10"/>
+      <c r="A2" s="10"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="12"/>
     </row>
     <row r="4" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
@@ -1151,16 +1420,16 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="C5" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1172,21 +1441,21 @@
         <v>38</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>7</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>7</v>
@@ -1194,27 +1463,27 @@
     </row>
     <row r="8" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>12</v>
@@ -1222,16 +1491,58 @@
     </row>
     <row r="10" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>7</v>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1248,28 +1559,28 @@
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
     <col min="3" max="3" width="91.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="7"/>
+      <c r="A1" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="9"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="8"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="10"/>
+      <c r="A2" s="10"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="12"/>
     </row>
     <row r="4" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
@@ -1286,157 +1597,903 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B6" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>12</v>
+      <c r="B10" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D2"/>
+  </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ACF71E1-1A7B-4AE6-BC58-BD85F84FA24C}">
+  <sheetPr>
+    <tabColor rgb="FF7030A0"/>
+  </sheetPr>
+  <dimension ref="A1:D27"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.109375" customWidth="1"/>
+    <col min="2" max="2" width="28.5546875" customWidth="1"/>
+    <col min="3" max="3" width="96.33203125" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="9"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="10"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="12"/>
+    </row>
+    <row r="4" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="A6" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="A7" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D7" s="1" t="s">
+    </row>
+    <row r="15" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>7</v>
       </c>
     </row>
+    <row r="18" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D2"/>
+  </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A1651D7-C889-456A-8F19-D382899C00A8}">
+  <sheetPr>
+    <tabColor rgb="FF7030A0"/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="3" width="87.6640625" customWidth="1"/>
+    <col min="4" max="4" width="9.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="9"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="10"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="12"/>
+    </row>
+    <row r="4" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
     <row r="8" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>7</v>
+      <c r="A8" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>7</v>
+      <c r="A9" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>7</v>
+      <c r="A10" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D11" s="1" t="s">
+      <c r="A11" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>7</v>
+      <c r="A12" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>7</v>
+      <c r="A13" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>7</v>
+      <c r="A14" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>7</v>
+      <c r="D16" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
